--- a/AAAGameData/DataTables/BulletTable.xlsx
+++ b/AAAGameData/DataTables/BulletTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>#</t>
   </si>
@@ -56,10 +56,16 @@
     </r>
   </si>
   <si>
+    <t>Speed</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>备注</t>
@@ -68,7 +74,15 @@
     <t>子弹实体预制体</t>
   </si>
   <si>
+    <t>子弹速度</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>子弹</t>
     </r>
     <r>
@@ -1242,8 +1256,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="30.8181818181818" customWidth="1"/>
   </cols>
@@ -1256,7 +1270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1266,46 +1280,58 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="2:5">
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D1 E1:X1">
+    <dataValidation type="list" allowBlank="1" sqref="D1:X1">
       <formula1>"i18n"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D3 E3:X3">
+    <dataValidation type="list" sqref="D3:X3">
       <formula1>"double,int,bool,string,float,enum,string[],uint,short,Vector2[],Vector3Int[],int4[],int4,Vector3Int,Vector3,Vector4[],Vector2,Vector4,Color,Color32,Vector2Int,Vector3[],Vector2Int[],Type,long[],bool[],int[],float[],double[],float[][],decimal,double[][]"</formula1>
     </dataValidation>
   </dataValidations>
